--- a/data/PIRL-Team-Database.xlsx
+++ b/data/PIRL-Team-Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentuml-my.sharepoint.com/personal/jiabin_shen_uml_edu/Documents/Research/Lab/Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="8_{60389376-1644-E24C-8482-050986915294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA4236A0-DBF0-A34A-8CB5-86B9A99D8ECC}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_9585E1FC1DC8A59F83486DA983AFA05085CCC031" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAE0FAB5-0CE7-9443-8311-9E09758A0A31}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="29920" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="38400" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Read Me First" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,424 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="202">
+  <si>
+    <t>Section</t>
+  </si>
+  <si>
+    <t>Order</t>
+  </si>
+  <si>
+    <t>Full Name</t>
+  </si>
+  <si>
+    <t>Role / Title</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Current Focus (short, for hover card)</t>
+  </si>
+  <si>
+    <t>Full Bio (for click-to-open pop-up)</t>
+  </si>
+  <si>
+    <t>Photo filename (see Photo Instructions tab)</t>
+  </si>
+  <si>
+    <t>Avatar initials (used if no photo)</t>
+  </si>
+  <si>
+    <t>Link 1 label</t>
+  </si>
+  <si>
+    <t>Link 1 URL</t>
+  </si>
+  <si>
+    <t>Link 2 label</t>
+  </si>
+  <si>
+    <t>Link 2 URL</t>
+  </si>
+  <si>
+    <t>Program (Degree – Department)</t>
+  </si>
+  <si>
+    <t>Years in Lab</t>
+  </si>
+  <si>
+    <t>Featured (full card vs. text line)</t>
+  </si>
+  <si>
+    <t>Current Members</t>
+  </si>
+  <si>
+    <t>Jiabin Shen, PhD</t>
+  </si>
+  <si>
+    <t>Principal Investigator</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>TBI rehabilitation · injury epidemiology · neurodivergent youth</t>
+  </si>
+  <si>
+    <t>Dr. Shen has studied pediatric injury prevention and rehabilitation since 2011. He directs the Pediatric Injury Research Lab at UMass Lowell, where his interdisciplinary program integrates virtual reality, fNIRS, and large-scale national datasets to improve outcomes for children with TBI, ADHD, and autism. Over $1.6M in external funding secured, 69 peer-reviewed publications, and 43 students mentored at UML. Dr. Shen received his PhD in Life-Span Developmental Psychology from University of Alabama at Birmingham (2015).</t>
+  </si>
+  <si>
+    <t>jiabin-shen.jpg</t>
+  </si>
+  <si>
+    <t>JS</t>
+  </si>
+  <si>
+    <t>UML Profile</t>
+  </si>
+  <si>
+    <t>https://www.uml.edu/fahss/psychology/faculty/shen-jiabin.aspx</t>
+  </si>
+  <si>
+    <t>Google Scholar</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?hl=en&amp;user=PZkRpx8AAAAJ&amp;view_op=list_works&amp;sortby=pubdate</t>
+  </si>
+  <si>
+    <t>Angelina Davis</t>
+  </si>
+  <si>
+    <t>PhD in Psychology · Lab Manager</t>
+  </si>
+  <si>
+    <t>Cognitive development · TBI · ASD · mental health</t>
+  </si>
+  <si>
+    <t>Lab Manager and PhD student in Psychology. Research interests include cognitive development, traumatic brain injuries, autism spectrum disorder, and mental health promotion in children. Presented at the APA 2024 conference ("Memory Impairment after Sports-Related TBI in Pediatric and Young Adult Athletes: A Scoping Review") and the NEPA 2024 conference ("Activity Level Predicts Injury History in Children"), plus the UML Psychology Research Symposium in May 2025 and May 2026. B.A. Neuroscience &amp; Psychology, Assumption University (2023).</t>
+  </si>
+  <si>
+    <t>angelina-davis.jpg</t>
+  </si>
+  <si>
+    <t>AD</t>
+  </si>
+  <si>
+    <t>Alumni</t>
+  </si>
+  <si>
+    <t>Jai Aravala</t>
+  </si>
+  <si>
+    <t>Masters in Public Health</t>
+  </si>
+  <si>
+    <t>Population health · injury disparities</t>
+  </si>
+  <si>
+    <t>Master of Public Health student contributing to the lab's population-based research on pediatric injury disparities and health outcomes.</t>
+  </si>
+  <si>
+    <t>jai-aravala.jpg</t>
+  </si>
+  <si>
+    <t>JA</t>
+  </si>
+  <si>
+    <t>Master's – Public Health</t>
+  </si>
+  <si>
+    <t>2023–2025</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Tonghui Xu</t>
+  </si>
+  <si>
+    <t>Doctor of Education</t>
+  </si>
+  <si>
+    <t>ASD injury risk · MEPS analysis</t>
+  </si>
+  <si>
+    <t>Doctoral graduate in Research &amp; Evaluation in Education. Presented "Identifying Crucial Predictors for Injury Risk in Children with ASD Using 22 Years of MEPS Data" at the American Public Health Association (APHA) annual conference, December 2024.</t>
+  </si>
+  <si>
+    <t>tonghui-xu.jpg</t>
+  </si>
+  <si>
+    <t>TX</t>
+  </si>
+  <si>
+    <t>Doctoral – Research &amp; Evaluation in Education</t>
+  </si>
+  <si>
+    <t>2023–2024</t>
+  </si>
+  <si>
+    <t>Skylar Charles</t>
+  </si>
+  <si>
+    <t>BA in Psychology</t>
+  </si>
+  <si>
+    <t>TBI in multilingual populations</t>
+  </si>
+  <si>
+    <t>UML psychology graduate. Presented "The Effects of Traumatic Brain Injury in Individual Languages of Multilinguals: A Systematic Review" at the New England Psychological Association (NEPA) conference, November 2024.</t>
+  </si>
+  <si>
+    <t>skylar-charles.jpg</t>
+  </si>
+  <si>
+    <t>SC</t>
+  </si>
+  <si>
+    <t>Undergraduate – Psychology</t>
+  </si>
+  <si>
+    <t>Alexandria Winstead</t>
+  </si>
+  <si>
+    <t>Mentored Research (Meta-Analysis of TBI Cognitive Training); FAHSS Student Assistantship</t>
+  </si>
+  <si>
+    <t>Doctoral – Applied Psychology &amp; Prevention Science</t>
+  </si>
+  <si>
+    <t>2021–2024</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Alex Clinton</t>
+  </si>
+  <si>
+    <t>Mentored Research (Donahue Humanities Ethics Fellowship); FAHSS Student Assistantship</t>
+  </si>
+  <si>
+    <t>2020–2024</t>
+  </si>
+  <si>
+    <t>Nayantara Kurpad</t>
+  </si>
+  <si>
+    <t>Mentored Research (Meta-Analytic SEM for Injury Prevention)</t>
+  </si>
+  <si>
+    <t>2020–2021</t>
+  </si>
+  <si>
+    <t>David Schena</t>
+  </si>
+  <si>
+    <t>Elyas Irankhah</t>
+  </si>
+  <si>
+    <t>Mentored Research (Machine Learning for Pediatric TBI Diagnosis), co-mentor</t>
+  </si>
+  <si>
+    <t>Doctoral – Mechanical Engineering</t>
+  </si>
+  <si>
+    <t>2021–2025</t>
+  </si>
+  <si>
+    <t>Amanda Carmichael</t>
+  </si>
+  <si>
+    <t>Mentored Research (Donahue Humanities Ethics Fellowship); NURS.7390 Mentored Research Course</t>
+  </si>
+  <si>
+    <t>Doctoral – Nursing</t>
+  </si>
+  <si>
+    <t>2022–2025</t>
+  </si>
+  <si>
+    <t>Joy Gomes</t>
+  </si>
+  <si>
+    <t>Thesis Chair</t>
+  </si>
+  <si>
+    <t>Master's – Applied Behavior Analysis &amp; Autism Studies</t>
+  </si>
+  <si>
+    <t>2024–</t>
+  </si>
+  <si>
+    <t>Evagelia C. Anthony</t>
+  </si>
+  <si>
+    <t>MA Community Social Psychology</t>
+  </si>
+  <si>
+    <t>Master's – Community Social Psychology</t>
+  </si>
+  <si>
+    <t>2022–2023</t>
+  </si>
+  <si>
+    <t>Shelby Kosterman</t>
+  </si>
+  <si>
+    <t>Moloney Scholar Fellow, Public Health Intern</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>Samantha Peters</t>
+  </si>
+  <si>
+    <t>Public Health Intern</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>Kathryn Smolag</t>
+  </si>
+  <si>
+    <t>Sara Avdulla</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>Loreynis FigueroaBrito</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>Venkata Shashidhar Akella</t>
+  </si>
+  <si>
+    <t>MS Engineering, co-mentor</t>
+  </si>
+  <si>
+    <t>Master's – Mechanical Engineering</t>
+  </si>
+  <si>
+    <t>Jesus Santiago</t>
+  </si>
+  <si>
+    <t>Emerging Scholars Program, Volunteer</t>
+  </si>
+  <si>
+    <t>Diya Patel</t>
+  </si>
+  <si>
+    <t>Lab Volunteer</t>
+  </si>
+  <si>
+    <t>2025–</t>
+  </si>
+  <si>
+    <t>Nicolas Spiegel</t>
+  </si>
+  <si>
+    <t>Research Service Learning</t>
+  </si>
+  <si>
+    <t>Quynh Pham</t>
+  </si>
+  <si>
+    <t>Moloney Scholar Fellow, Emerging Scholars Program</t>
+  </si>
+  <si>
+    <t>2024–2025</t>
+  </si>
+  <si>
+    <t>Benjamin Hickman</t>
+  </si>
+  <si>
+    <t>Ashley Cline</t>
+  </si>
+  <si>
+    <t>Arthur Chigas</t>
+  </si>
+  <si>
+    <t>Research Service Learning, co-mentor</t>
+  </si>
+  <si>
+    <t>Joseph Chaghouri</t>
+  </si>
+  <si>
+    <t>Meher Kaur</t>
+  </si>
+  <si>
+    <t>Julia Harrington</t>
+  </si>
+  <si>
+    <t>Honors Directed Study</t>
+  </si>
+  <si>
+    <t>Racksa Sim</t>
+  </si>
+  <si>
+    <t>Ronald Creed</t>
+  </si>
+  <si>
+    <t>Gayathri Dayashankar</t>
+  </si>
+  <si>
+    <t>Directed Study / Research Service Learning</t>
+  </si>
+  <si>
+    <t>Jack Blake</t>
+  </si>
+  <si>
+    <t>Emerging Scholars Program</t>
+  </si>
+  <si>
+    <t>2021–2022</t>
+  </si>
+  <si>
+    <t>Hailey DuBose</t>
+  </si>
+  <si>
+    <t>Research Service Learning / Directed Study</t>
+  </si>
+  <si>
+    <t>Vy Phan</t>
+  </si>
+  <si>
+    <t>Dejonai Willis</t>
+  </si>
+  <si>
+    <t>Honors College Fellowship Program</t>
+  </si>
+  <si>
+    <t>Lauren Field</t>
+  </si>
+  <si>
+    <t>Mentored Research, co-mentor</t>
+  </si>
+  <si>
+    <t>Undergraduate – Physical Therapy &amp; Kinesiology</t>
+  </si>
+  <si>
+    <t>Kyra Barry</t>
+  </si>
+  <si>
+    <t>Undergraduate – Nursing</t>
+  </si>
+  <si>
+    <t>Maika Belizor</t>
+  </si>
+  <si>
+    <t>River Hawk Scholars Academy Road to Research program</t>
+  </si>
+  <si>
+    <t>Undergraduate – Biological Sciences</t>
+  </si>
   <si>
     <t>Pediatric Injury Research Lab — Team Database</t>
   </si>
@@ -88,136 +505,58 @@
     <t>Step-by-step for adding real headshot photos instead of initials.</t>
   </si>
   <si>
-    <t>Section</t>
-  </si>
-  <si>
-    <t>Order</t>
-  </si>
-  <si>
-    <t>Full Name</t>
-  </si>
-  <si>
-    <t>Role / Title</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Current Focus (short, for hover card)</t>
-  </si>
-  <si>
-    <t>Full Bio (for click-to-open pop-up)</t>
-  </si>
-  <si>
-    <t>Photo filename (see Photo Instructions tab)</t>
-  </si>
-  <si>
-    <t>Avatar initials (used if no photo)</t>
-  </si>
-  <si>
-    <t>Link 1 label</t>
-  </si>
-  <si>
-    <t>Link 1 URL</t>
-  </si>
-  <si>
-    <t>Link 2 label</t>
-  </si>
-  <si>
-    <t>Link 2 URL</t>
-  </si>
-  <si>
-    <t>Current Members</t>
-  </si>
-  <si>
-    <t>Jiabin Shen, PhD</t>
-  </si>
-  <si>
-    <t>Principal Investigator</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>TBI rehabilitation · injury epidemiology · neurodivergent youth</t>
-  </si>
-  <si>
-    <t>jiabin-shen.jpg</t>
-  </si>
-  <si>
-    <t>JS</t>
-  </si>
-  <si>
-    <t>UML Profile</t>
-  </si>
-  <si>
-    <t>https://www.uml.edu/fahss/psychology/faculty/shen-jiabin.aspx</t>
-  </si>
-  <si>
-    <t>Google Scholar</t>
-  </si>
-  <si>
-    <t>https://scholar.google.com/citations?hl=en&amp;user=PZkRpx8AAAAJ&amp;view_op=list_works&amp;sortby=pubdate</t>
-  </si>
-  <si>
-    <t>Angelina Davis</t>
-  </si>
-  <si>
-    <t>Cognitive development · TBI · ASD · mental health</t>
-  </si>
-  <si>
-    <t>angelina-davis.jpg</t>
-  </si>
-  <si>
-    <t>AD</t>
-  </si>
-  <si>
-    <t>Jai Aravala</t>
-  </si>
-  <si>
-    <t>Population health · injury disparities</t>
-  </si>
-  <si>
-    <t>Master of Public Health student contributing to the lab's population-based research on pediatric injury disparities and health outcomes.</t>
-  </si>
-  <si>
-    <t>jai-aravala.jpg</t>
-  </si>
-  <si>
-    <t>JA</t>
-  </si>
-  <si>
-    <t>Alumni</t>
-  </si>
-  <si>
-    <t>Tonghui Xu</t>
-  </si>
-  <si>
-    <t>ASD injury risk · MEPS analysis</t>
-  </si>
-  <si>
-    <t>Doctoral graduate in Research &amp; Evaluation in Education. Presented "Identifying Crucial Predictors for Injury Risk in Children with ASD Using 22 Years of MEPS Data" at the American Public Health Association (APHA) annual conference, December 2024.</t>
-  </si>
-  <si>
-    <t>tonghui-xu.jpg</t>
-  </si>
-  <si>
-    <t>TX</t>
-  </si>
-  <si>
-    <t>Skylar Charles</t>
-  </si>
-  <si>
-    <t>TBI in multilingual populations</t>
-  </si>
-  <si>
-    <t>UML psychology graduate. Presented "The Effects of Traumatic Brain Injury in Individual Languages of Multilinguals: A Systematic Review" at the New England Psychological Association (NEPA) conference, November 2024.</t>
-  </si>
-  <si>
-    <t>skylar-charles.jpg</t>
-  </si>
-  <si>
-    <t>SC</t>
+    <t>New: Alumni columns (Program / Years in Lab / Featured)</t>
+  </si>
+  <si>
+    <t>1.  'Program (Degree – Department)' and 'Years in Lab' are short facts only —</t>
+  </si>
+  <si>
+    <t>e.g. "Doctoral – Applied Psychology &amp; Prevention Science" and "2021–2024".</t>
+  </si>
+  <si>
+    <t>2.  'Featured' = Yes means the person gets a full card (bio, focus, photo/initials, links),</t>
+  </si>
+  <si>
+    <t>same as today. 'Featured' = No means a plain text line only: Name — Program, Years, Role.</t>
+  </si>
+  <si>
+    <t>3.  You choose who is Featured. There's no rule — just set the column to Yes or No per person.</t>
+  </si>
+  <si>
+    <t>4.  For 'No' rows: leave Photo filename, Avatar initials, Focus, and Bio blank.</t>
+  </si>
+  <si>
+    <t>No placeholder image or initials circle is used for these — just the text line.</t>
+  </si>
+  <si>
+    <t>A note on the new Alumni rows</t>
+  </si>
+  <si>
+    <t>Most alumni listed here have graduated and could not be reached to confirm they're</t>
+  </si>
+  <si>
+    <t>comfortable being listed. Per your instruction, entries are limited to facts already on your</t>
+  </si>
+  <si>
+    <t>CV (program, years, mentoring role) — no photos, and no current employer/position unless</t>
+  </si>
+  <si>
+    <t>the person told you directly. The website includes a line inviting former lab members to</t>
+  </si>
+  <si>
+    <t>contact you to update or remove their listing.</t>
+  </si>
+  <si>
+    <t>Scope rule used: only people with a direct mentoring role (Research Service Learning,</t>
+  </si>
+  <si>
+    <t>Directed Study, Emerging Scholars, Mentored Research, Thesis/Dissertation Chair, etc.)</t>
+  </si>
+  <si>
+    <t>are listed. Students where Dr. Shen's only role was QP/dissertation committee member</t>
+  </si>
+  <si>
+    <t>(not primary mentor) are excluded. Source: Shen CV, Student Mentoring section.</t>
   </si>
   <si>
     <t>Allowed values</t>
@@ -229,6 +568,9 @@
     <t>Status (must match exactly)</t>
   </si>
   <si>
+    <t>Featured (must match exactly)</t>
+  </si>
+  <si>
     <t>Note: typing a Section or Status value that doesn't match one of these exactly will cause</t>
   </si>
   <si>
@@ -287,24 +629,6 @@
   </si>
   <si>
     <t>If a photo filename is left blank, that person will simply show initials — nothing breaks.</t>
-  </si>
-  <si>
-    <t>PhD in Psychology · Lab Manager</t>
-  </si>
-  <si>
-    <t>Masters in Public Health</t>
-  </si>
-  <si>
-    <t>Doctor of Education</t>
-  </si>
-  <si>
-    <t>BA in Psychology</t>
-  </si>
-  <si>
-    <t>Dr. Shen has studied pediatric injury prevention and rehabilitation since 2011. He directs the Pediatric Injury Research Lab at UMass Lowell, where his interdisciplinary program integrates virtual reality, fNIRS, and large-scale national datasets to improve outcomes for children with TBI, ADHD, and autism. Over $1.6M in external funding secured, 69 peer-reviewed publications, and 43 students mentored at UML. Dr. Shen received his PhD in Life-Span Developmental Psychology from University of Alabama at Birmingham (2015).</t>
-  </si>
-  <si>
-    <t>Lab Manager and PhD student in Psychology. Research interests include cognitive development, traumatic brain injuries, autism spectrum disorder, and mental health promotion in children. Presented at the APA 2024 conference ("Memory Impairment after Sports-Related TBI in Pediatric and Young Adult Athletes: A Scoping Review") and the NEPA 2024 conference ("Activity Level Predicts Injury History in Children"), plus the UML Psychology Research Symposium in May 2025 and May 2026. B.A. Neuroscience &amp; Psychology, Assumption University (2023).</t>
   </si>
 </sst>
 </file>
@@ -414,7 +738,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -423,15 +747,16 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -734,7 +1059,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:C24"/>
+  <dimension ref="B2:C47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -743,14 +1068,14 @@
     <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" ht="20" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" ht="16" x14ac:dyDescent="0.2">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
-        <v>1</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.2">
@@ -758,7 +1083,7 @@
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
-        <v>2</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.2">
@@ -766,52 +1091,52 @@
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
-        <v>3</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B9" s="3" t="s">
-        <v>4</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B10" s="3" t="s">
-        <v>5</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B11" s="3" t="s">
-        <v>6</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B12" s="3" t="s">
-        <v>7</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
-        <v>8</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B14" s="3" t="s">
-        <v>9</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B15" s="3" t="s">
-        <v>10</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B16" s="3" t="s">
-        <v>11</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B17" s="3" t="s">
-        <v>12</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -819,36 +1144,126 @@
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
-        <v>14</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B22" s="4" t="s">
-        <v>15</v>
+        <v>154</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>16</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B23" s="4" t="s">
-        <v>17</v>
+        <v>156</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>18</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B24" s="4" t="s">
-        <v>19</v>
+        <v>158</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>20</v>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B26" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B28" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C29" s="9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B30" s="9" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C31" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B32" s="9" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B33" s="9" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C34" s="9" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B36" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B38" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C39" s="9" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C40" s="9" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C41" s="9" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C42" s="9" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B44" s="9" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C45" s="9" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C46" s="9" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C47" s="9" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -858,7 +1273,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:P40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -873,230 +1288,1433 @@
     <col min="10" max="10" width="14" customWidth="1"/>
     <col min="11" max="11" width="34" customWidth="1"/>
     <col min="12" max="12" width="14" customWidth="1"/>
-    <col min="13" max="13" width="34" customWidth="1"/>
+    <col min="13" max="14" width="34" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="16" max="16" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="8">
+        <v>1</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="H2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="I2" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="J2" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="K2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="L2" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="M2" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+    </row>
+    <row r="3" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="8">
+        <v>2</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="D3" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="E3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="G3" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="H3" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="I3" s="8" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="6">
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="11"/>
+    </row>
+    <row r="4" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="8">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C4" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D4" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E4" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="G4" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="H4" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="O4" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="P4" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="8">
+        <v>2</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="P5" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="8">
+        <v>3</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="O6" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="P6" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A7" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="11">
+        <v>4</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="O7" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="P7" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A8" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="11">
+        <v>5</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="O8" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="P8" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A9" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="11">
+        <v>6</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="O9" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="P9" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A10" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="11">
+        <v>7</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="O10" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="P10" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A11" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="11">
+        <v>8</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="O11" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="P11" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A12" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="11">
+        <v>9</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="O12" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="P12" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A13" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="11">
+        <v>10</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="O13" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="P13" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A14" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="11">
+        <v>11</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="O14" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="P14" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A15" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="11">
+        <v>12</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="O15" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="P15" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A16" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="11">
+        <v>13</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="O16" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="H2" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J2" s="6" t="s">
+      <c r="P16" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A17" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="11">
+        <v>14</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="K2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="6">
-        <v>2</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="E3" s="6" t="s">
+      <c r="O17" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="P17" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A18" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="11">
+        <v>15</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="O18" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="P18" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A19" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="11">
+        <v>16</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="O19" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="P19" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A20" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="11">
+        <v>17</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="O20" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="P20" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A21" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="11">
+        <v>18</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="O21" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="P21" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A22" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="11">
+        <v>19</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="O22" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="P22" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A23" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="11">
+        <v>20</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="O23" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="P23" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A24" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="11">
+        <v>21</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="O24" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="P24" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A25" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="11">
+        <v>22</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="O25" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="P25" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A26" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="11">
+        <v>23</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="O26" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="P26" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A27" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="11">
+        <v>24</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="O27" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="P27" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A28" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="11">
+        <v>25</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+      <c r="N28" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="O28" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="P28" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A29" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="11">
+        <v>26</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="O29" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="P29" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A30" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="11">
+        <v>27</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="O30" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="P30" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A31" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="11">
+        <v>28</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="O31" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="P31" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A32" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="11">
+        <v>29</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="O32" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="P32" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A33" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="11">
+        <v>30</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="O33" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="P33" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A34" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" s="11">
+        <v>31</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="O34" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="P34" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A35" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="11">
+        <v>32</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="O35" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="P35" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A36" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="11">
+        <v>33</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+      <c r="N36" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="O36" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="P36" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A37" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B37" s="11">
+        <v>34</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+      <c r="N37" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="O37" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="P37" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A38" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B38" s="11">
+        <v>35</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
+      <c r="N38" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="O38" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="P38" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A39" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" s="11">
+        <v>36</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+      <c r="N39" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="O39" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="P39" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A40" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B40" s="11">
         <v>37</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-    </row>
-    <row r="4" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4" s="6">
-        <v>1</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="G4" s="6" t="s">
+      <c r="C40" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+      <c r="M40" s="11"/>
+      <c r="N40" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="O40" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="H4" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-    </row>
-    <row r="5" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B5" s="6">
-        <v>2</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-    </row>
-    <row r="6" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B6" s="6">
-        <v>3</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
+      <c r="P40" s="11" t="s">
+        <v>63</v>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="A2:A999" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Current Members,Research Collaborators,Alumni"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="E2:E999" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Active,Alumni,On Leave"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="P2:P999" xr:uid="{00000000-0002-0000-0100-000002000000}">
+      <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1105,52 +2723,62 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B2:D10"/>
+  <dimension ref="B2:F10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="3" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B4" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B4" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B9" s="8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B10" s="8" t="s">
-        <v>69</v>
+        <v>34</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B9" s="7" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B10" s="7" t="s">
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -1167,9 +2795,9 @@
     <col min="2" max="2" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" ht="20" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
-        <v>70</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.2">
@@ -1177,12 +2805,12 @@
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B4" s="3" t="s">
-        <v>71</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
-        <v>72</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.2">
@@ -1190,7 +2818,7 @@
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
-        <v>73</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.2">
@@ -1198,12 +2826,12 @@
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B9" s="3" t="s">
-        <v>74</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B10" s="3" t="s">
-        <v>75</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.2">
@@ -1211,7 +2839,7 @@
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B12" s="3" t="s">
-        <v>76</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.2">
@@ -1219,17 +2847,17 @@
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B14" s="3" t="s">
-        <v>77</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B15" s="3" t="s">
-        <v>78</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B16" s="3" t="s">
-        <v>79</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.2">
@@ -1237,12 +2865,12 @@
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B18" s="3" t="s">
-        <v>80</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B19" s="3" t="s">
-        <v>81</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.2">
@@ -1250,7 +2878,7 @@
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
-        <v>82</v>
+        <v>196</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.2">
@@ -1258,12 +2886,12 @@
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B23" s="3" t="s">
-        <v>83</v>
+        <v>197</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B24" s="3" t="s">
-        <v>84</v>
+        <v>198</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.2">
@@ -1271,12 +2899,12 @@
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B26" s="3" t="s">
-        <v>85</v>
+        <v>199</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B27" s="3" t="s">
-        <v>86</v>
+        <v>200</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.2">
@@ -1284,7 +2912,7 @@
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B29" s="3" t="s">
-        <v>87</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>

--- a/data/PIRL-Team-Database.xlsx
+++ b/data/PIRL-Team-Database.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentuml-my.sharepoint.com/personal/jiabin_shen_uml_edu/Documents/Research/Lab/Website/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentuml-my.sharepoint.com/personal/jiabin_shen_uml_edu/Documents/Research/Lab/Website/github/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_9585E1FC1DC8A59F83486DA983AFA05085CCC031" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAE0FAB5-0CE7-9443-8311-9E09758A0A31}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_9585E1FC1DC8A59F83486DA983AFA05085CCC031" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B3F3060-8C85-DB48-A0ED-73D5CC6FBC04}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="38400" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -265,9 +265,6 @@
     <t>Joy Gomes</t>
   </si>
   <si>
-    <t>Thesis Chair</t>
-  </si>
-  <si>
     <t>Master's – Applied Behavior Analysis &amp; Autism Studies</t>
   </si>
   <si>
@@ -629,6 +626,9 @@
   </si>
   <si>
     <t>If a photo filename is left blank, that person will simply show initials — nothing breaks.</t>
+  </si>
+  <si>
+    <t>ABAAS Masters Student</t>
   </si>
 </sst>
 </file>
@@ -738,7 +738,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -757,6 +757,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1070,12 +1071,12 @@
   <sheetData>
     <row r="2" spans="2:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="2:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.2">
@@ -1083,7 +1084,7 @@
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.2">
@@ -1091,52 +1092,52 @@
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B9" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B10" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B11" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B12" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B14" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B15" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B16" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B17" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -1144,126 +1145,126 @@
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B22" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B23" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B24" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="16" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B28" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C29" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B30" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C31" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B32" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B33" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C34" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="36" spans="2:3" ht="16" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B38" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C39" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C40" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C41" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C42" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B44" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C45" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C46" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C47" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -1763,8 +1764,8 @@
       <c r="C13" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="D13" s="11" t="s">
-        <v>80</v>
+      <c r="D13" s="12" t="s">
+        <v>201</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>19</v>
@@ -1778,10 +1779,10 @@
       <c r="L13" s="11"/>
       <c r="M13" s="11"/>
       <c r="N13" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="O13" s="11" t="s">
         <v>81</v>
-      </c>
-      <c r="O13" s="11" t="s">
-        <v>82</v>
       </c>
       <c r="P13" s="11" t="s">
         <v>43</v>
@@ -1795,10 +1796,10 @@
         <v>11</v>
       </c>
       <c r="C14" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="11" t="s">
         <v>83</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>84</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>34</v>
@@ -1812,10 +1813,10 @@
       <c r="L14" s="11"/>
       <c r="M14" s="11"/>
       <c r="N14" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="O14" s="11" t="s">
         <v>85</v>
-      </c>
-      <c r="O14" s="11" t="s">
-        <v>86</v>
       </c>
       <c r="P14" s="11" t="s">
         <v>63</v>
@@ -1829,10 +1830,10 @@
         <v>12</v>
       </c>
       <c r="C15" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" s="11" t="s">
         <v>87</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>88</v>
       </c>
       <c r="E15" s="11" t="s">
         <v>34</v>
@@ -1849,7 +1850,7 @@
         <v>41</v>
       </c>
       <c r="O15" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P15" s="11" t="s">
         <v>63</v>
@@ -1863,10 +1864,10 @@
         <v>13</v>
       </c>
       <c r="C16" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>90</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>91</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>34</v>
@@ -1883,7 +1884,7 @@
         <v>41</v>
       </c>
       <c r="O16" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P16" s="11" t="s">
         <v>63</v>
@@ -1897,10 +1898,10 @@
         <v>14</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>34</v>
@@ -1917,7 +1918,7 @@
         <v>41</v>
       </c>
       <c r="O17" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P17" s="11" t="s">
         <v>63</v>
@@ -1931,10 +1932,10 @@
         <v>15</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>34</v>
@@ -1951,7 +1952,7 @@
         <v>41</v>
       </c>
       <c r="O18" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P18" s="11" t="s">
         <v>63</v>
@@ -1965,10 +1966,10 @@
         <v>16</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>34</v>
@@ -1985,7 +1986,7 @@
         <v>41</v>
       </c>
       <c r="O19" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P19" s="11" t="s">
         <v>63</v>
@@ -1999,10 +2000,10 @@
         <v>17</v>
       </c>
       <c r="C20" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>98</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>99</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>34</v>
@@ -2016,7 +2017,7 @@
       <c r="L20" s="11"/>
       <c r="M20" s="11"/>
       <c r="N20" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O20" s="11" t="s">
         <v>78</v>
@@ -2033,10 +2034,10 @@
         <v>18</v>
       </c>
       <c r="C21" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D21" s="11" t="s">
         <v>101</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>102</v>
       </c>
       <c r="E21" s="11" t="s">
         <v>34</v>
@@ -2053,7 +2054,7 @@
         <v>58</v>
       </c>
       <c r="O21" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P21" s="11" t="s">
         <v>63</v>
@@ -2067,10 +2068,10 @@
         <v>19</v>
       </c>
       <c r="C22" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D22" s="11" t="s">
         <v>103</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>104</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>34</v>
@@ -2087,7 +2088,7 @@
         <v>58</v>
       </c>
       <c r="O22" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P22" s="11" t="s">
         <v>63</v>
@@ -2101,10 +2102,10 @@
         <v>20</v>
       </c>
       <c r="C23" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D23" s="11" t="s">
         <v>106</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>107</v>
       </c>
       <c r="E23" s="11" t="s">
         <v>34</v>
@@ -2121,7 +2122,7 @@
         <v>58</v>
       </c>
       <c r="O23" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P23" s="11" t="s">
         <v>63</v>
@@ -2135,10 +2136,10 @@
         <v>21</v>
       </c>
       <c r="C24" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" s="11" t="s">
         <v>108</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>109</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>34</v>
@@ -2155,7 +2156,7 @@
         <v>58</v>
       </c>
       <c r="O24" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P24" s="11" t="s">
         <v>63</v>
@@ -2169,10 +2170,10 @@
         <v>22</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>34</v>
@@ -2189,7 +2190,7 @@
         <v>58</v>
       </c>
       <c r="O25" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P25" s="11" t="s">
         <v>63</v>
@@ -2203,10 +2204,10 @@
         <v>23</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>34</v>
@@ -2223,7 +2224,7 @@
         <v>58</v>
       </c>
       <c r="O26" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P26" s="11" t="s">
         <v>63</v>
@@ -2237,10 +2238,10 @@
         <v>24</v>
       </c>
       <c r="C27" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="D27" s="11" t="s">
         <v>113</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>114</v>
       </c>
       <c r="E27" s="11" t="s">
         <v>34</v>
@@ -2257,7 +2258,7 @@
         <v>58</v>
       </c>
       <c r="O27" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P27" s="11" t="s">
         <v>63</v>
@@ -2271,10 +2272,10 @@
         <v>25</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>34</v>
@@ -2291,7 +2292,7 @@
         <v>58</v>
       </c>
       <c r="O28" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P28" s="11" t="s">
         <v>63</v>
@@ -2305,10 +2306,10 @@
         <v>26</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E29" s="11" t="s">
         <v>34</v>
@@ -2325,7 +2326,7 @@
         <v>58</v>
       </c>
       <c r="O29" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P29" s="11" t="s">
         <v>63</v>
@@ -2339,10 +2340,10 @@
         <v>27</v>
       </c>
       <c r="C30" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="D30" s="11" t="s">
         <v>117</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>118</v>
       </c>
       <c r="E30" s="11" t="s">
         <v>34</v>
@@ -2359,7 +2360,7 @@
         <v>58</v>
       </c>
       <c r="O30" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P30" s="11" t="s">
         <v>63</v>
@@ -2373,10 +2374,10 @@
         <v>28</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E31" s="11" t="s">
         <v>34</v>
@@ -2393,7 +2394,7 @@
         <v>58</v>
       </c>
       <c r="O31" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P31" s="11" t="s">
         <v>63</v>
@@ -2407,10 +2408,10 @@
         <v>29</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E32" s="11" t="s">
         <v>34</v>
@@ -2441,10 +2442,10 @@
         <v>30</v>
       </c>
       <c r="C33" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D33" s="11" t="s">
         <v>121</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>122</v>
       </c>
       <c r="E33" s="11" t="s">
         <v>34</v>
@@ -2461,7 +2462,7 @@
         <v>58</v>
       </c>
       <c r="O33" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P33" s="11" t="s">
         <v>63</v>
@@ -2475,10 +2476,10 @@
         <v>31</v>
       </c>
       <c r="C34" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="D34" s="11" t="s">
         <v>123</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>124</v>
       </c>
       <c r="E34" s="11" t="s">
         <v>34</v>
@@ -2495,7 +2496,7 @@
         <v>58</v>
       </c>
       <c r="O34" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P34" s="11" t="s">
         <v>63</v>
@@ -2509,10 +2510,10 @@
         <v>32</v>
       </c>
       <c r="C35" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="D35" s="11" t="s">
         <v>126</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>127</v>
       </c>
       <c r="E35" s="11" t="s">
         <v>34</v>
@@ -2529,7 +2530,7 @@
         <v>58</v>
       </c>
       <c r="O35" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P35" s="11" t="s">
         <v>63</v>
@@ -2543,10 +2544,10 @@
         <v>33</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E36" s="11" t="s">
         <v>34</v>
@@ -2563,7 +2564,7 @@
         <v>58</v>
       </c>
       <c r="O36" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P36" s="11" t="s">
         <v>63</v>
@@ -2577,10 +2578,10 @@
         <v>34</v>
       </c>
       <c r="C37" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D37" s="11" t="s">
         <v>129</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>130</v>
       </c>
       <c r="E37" s="11" t="s">
         <v>34</v>
@@ -2597,7 +2598,7 @@
         <v>58</v>
       </c>
       <c r="O37" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P37" s="11" t="s">
         <v>63</v>
@@ -2611,10 +2612,10 @@
         <v>35</v>
       </c>
       <c r="C38" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="D38" s="11" t="s">
         <v>131</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>132</v>
       </c>
       <c r="E38" s="11" t="s">
         <v>34</v>
@@ -2628,10 +2629,10 @@
       <c r="L38" s="11"/>
       <c r="M38" s="11"/>
       <c r="N38" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O38" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P38" s="11" t="s">
         <v>63</v>
@@ -2645,10 +2646,10 @@
         <v>36</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E39" s="11" t="s">
         <v>34</v>
@@ -2662,7 +2663,7 @@
       <c r="L39" s="11"/>
       <c r="M39" s="11"/>
       <c r="N39" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O39" s="11" t="s">
         <v>51</v>
@@ -2679,10 +2680,10 @@
         <v>37</v>
       </c>
       <c r="C40" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="D40" s="11" t="s">
         <v>136</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>137</v>
       </c>
       <c r="E40" s="11" t="s">
         <v>34</v>
@@ -2696,7 +2697,7 @@
       <c r="L40" s="11"/>
       <c r="M40" s="11"/>
       <c r="N40" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O40" s="11" t="s">
         <v>51</v>
@@ -2735,18 +2736,18 @@
   <sheetData>
     <row r="2" spans="2:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B4" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="F4" s="6" t="s">
         <v>180</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.2">
@@ -2773,12 +2774,12 @@
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B9" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B10" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -2797,7 +2798,7 @@
   <sheetData>
     <row r="2" spans="2:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.2">
@@ -2805,12 +2806,12 @@
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B4" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.2">
@@ -2818,7 +2819,7 @@
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.2">
@@ -2826,12 +2827,12 @@
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B9" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B10" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.2">
@@ -2839,7 +2840,7 @@
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B12" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.2">
@@ -2847,17 +2848,17 @@
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B14" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B15" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B16" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.2">
@@ -2865,12 +2866,12 @@
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B18" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B19" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.2">
@@ -2878,7 +2879,7 @@
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.2">
@@ -2886,12 +2887,12 @@
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B23" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B24" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.2">
@@ -2899,12 +2900,12 @@
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B26" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B27" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.2">
@@ -2912,7 +2913,7 @@
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B29" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/data/PIRL-Team-Database.xlsx
+++ b/data/PIRL-Team-Database.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C52"/>
+  <dimension ref="B2:C59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -519,11 +519,14 @@
   </cols>
   <sheetData>
     <row r="2" ht="20" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>Pediatric Injury Research Lab — Team Database</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="C3" s="10" t="n"/>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
@@ -531,9 +534,11 @@
           <t>How this works</t>
         </is>
       </c>
+      <c r="C4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="B5" s="3" t="n"/>
+      <c r="C5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
@@ -541,9 +546,11 @@
           <t>This workbook is the single source of truth for the 'Meet the Lab' section on your website.</t>
         </is>
       </c>
+      <c r="C6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="3" t="n"/>
+      <c r="C7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="3" t="inlineStr">
@@ -826,6 +833,48 @@
       <c r="C52" s="10" t="inlineStr">
         <is>
           <t>(not primary mentor) are excluded. Source: Shen CV, Student Mentoring section.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>6.  For Alumni, the website sorts automatically by 'Years in Lab' (most recent</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>first) within each Degree Level -- the 'Order' column is NOT used for Alumni, only</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>for Current Members. Add a new alumni row with the correct Years and it will appear</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>in the right place automatically -- no renumbering needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>An open-ended range like "2024-" means still ongoing -- if someone is still active,</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>they belong in Current Members, not Alumni.</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1119,7 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
@@ -1139,7 +1188,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
@@ -1208,7 +1257,7 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
@@ -1383,7 +1432,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
@@ -1436,7 +1485,7 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
@@ -1489,7 +1538,7 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
@@ -1542,7 +1591,7 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
@@ -1595,7 +1644,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
@@ -1604,7 +1653,7 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Master's Thesis</t>
+          <t>MS in Applied Behavior Analysis &amp; Autism Studies · Master's Thesis</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
@@ -1620,26 +1669,10 @@
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="12" t="n"/>
       <c r="M13" s="12" t="n"/>
-      <c r="N13" s="12" t="inlineStr">
-        <is>
-          <t>Master's</t>
-        </is>
-      </c>
-      <c r="O13" s="12" t="inlineStr">
-        <is>
-          <t>Applied Behavior Analysis &amp; Autism Studies</t>
-        </is>
-      </c>
-      <c r="P13" s="12" t="inlineStr">
-        <is>
-          <t>2024–</t>
-        </is>
-      </c>
-      <c r="Q13" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="N13" s="12" t="n"/>
+      <c r="O13" s="12" t="n"/>
+      <c r="P13" s="12" t="n"/>
+      <c r="Q13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -1648,7 +1681,7 @@
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
@@ -1701,7 +1734,7 @@
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
@@ -1754,7 +1787,7 @@
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
@@ -1807,7 +1840,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
@@ -1860,7 +1893,7 @@
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
@@ -1913,7 +1946,7 @@
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
@@ -1966,7 +1999,7 @@
         </is>
       </c>
       <c r="B20" s="12" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
@@ -2015,7 +2048,7 @@
         </is>
       </c>
       <c r="B21" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
@@ -2052,7 +2085,7 @@
       </c>
       <c r="P21" s="12" t="inlineStr">
         <is>
-          <t>2024–</t>
+          <t>2024–2025</t>
         </is>
       </c>
       <c r="Q21" s="12" t="inlineStr">
@@ -2068,7 +2101,7 @@
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
@@ -2105,7 +2138,7 @@
       </c>
       <c r="P22" s="12" t="inlineStr">
         <is>
-          <t>2025–</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="Q22" s="12" t="inlineStr">
@@ -2121,7 +2154,7 @@
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
@@ -2174,7 +2207,7 @@
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
@@ -2227,7 +2260,7 @@
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
@@ -2280,7 +2313,7 @@
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
@@ -2333,7 +2366,7 @@
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
@@ -2386,7 +2419,7 @@
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
@@ -2439,7 +2472,7 @@
         </is>
       </c>
       <c r="B29" s="12" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
@@ -2492,7 +2525,7 @@
         </is>
       </c>
       <c r="B30" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
@@ -2545,7 +2578,7 @@
         </is>
       </c>
       <c r="B31" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
@@ -2598,7 +2631,7 @@
         </is>
       </c>
       <c r="B32" s="12" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
@@ -2651,7 +2684,7 @@
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
@@ -2704,7 +2737,7 @@
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
@@ -2757,7 +2790,7 @@
         </is>
       </c>
       <c r="B35" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
@@ -2810,7 +2843,7 @@
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
@@ -2863,7 +2896,7 @@
         </is>
       </c>
       <c r="B37" s="12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
@@ -2916,7 +2949,7 @@
         </is>
       </c>
       <c r="B38" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
@@ -2969,7 +3002,7 @@
         </is>
       </c>
       <c r="B39" s="12" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
@@ -3022,7 +3055,7 @@
         </is>
       </c>
       <c r="B40" s="12" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
